--- a/reports/pdf_rolling5_20261014.xlsx
+++ b/reports/pdf_rolling5_20261014.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,163억   ·   현금 144억(2.8%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 11종목  /  매도 29종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,127억   ·   현금 72억(1.4%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 11종목  /  매도 29종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>301</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4548939402</v>
+        <v>4548939127</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-219</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2456769172</v>
+        <v>-2456769024</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>247</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1537200118</v>
+        <v>1537200025</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-112</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1889084526</v>
+        <v>-1889084412</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>133</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>10491522611</v>
+        <v>10491521976</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-80</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2382364865</v>
+        <v>-2382364721</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2041064341</v>
+        <v>2041064218</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-59</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1031978225</v>
+        <v>-1031978162</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>503348903</v>
+        <v>503348872</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-51</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-966344271</v>
+        <v>-966344213</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>27</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>945860294</v>
+        <v>945860236</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-46</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1718592824</v>
+        <v>-1718592720</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1744160634</v>
+        <v>1744160528</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-42</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-3883334011</v>
+        <v>-3883333776</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>983072357</v>
+        <v>983072298</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-30</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1831368665</v>
+        <v>-1831368554</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>526270741</v>
+        <v>526270709</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-28</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-326871559</v>
+        <v>-326871539</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>484400976</v>
+        <v>484400947</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-28</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1168191224</v>
+        <v>-1168191154</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1486500540</v>
+        <v>1486500450</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-26</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-858008112</v>
+        <v>-858008060</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>-23</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-511703036</v>
+        <v>-511703005</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1180,23 +1180,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-21</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1048874781</v>
+        <v>-1363120913</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>5.12%→5.45%</t>
+          <t>0.46%→0.12%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>573→552</t>
+          <t>30→9</t>
         </is>
       </c>
     </row>
@@ -1208,23 +1208,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-21</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1363120995</v>
+        <v>-1048874718</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.12%</t>
+          <t>5.12%→5.45%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>30→9</t>
+          <t>573→552</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
         <v>-13</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-87475602</v>
+        <v>-87475596</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-263407896</v>
+        <v>-263407880</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1292,23 +1292,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-561401704</v>
+        <v>-856818859</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>1.03%→0.74%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>11→0</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1320,23 +1320,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-856818911</v>
+        <v>-561401670</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.74%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>11→0</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
         <v>-10</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-844332307</v>
+        <v>-844332256</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-450905164</v>
+        <v>-450905136</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1404,23 +1404,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-894873325</v>
+        <v>-1284336389</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>4.88%→4.49%</t>
+          <t>6.79%→7.79%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>158→152</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1432,23 +1432,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-127244446</v>
+        <v>-1557852472</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.38%</t>
+          <t>0.57%→0.36%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>13→7</t>
         </is>
       </c>
     </row>
@@ -1460,23 +1460,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1557852566</v>
+        <v>-127244439</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.57%→0.36%</t>
+          <t>0.42%→0.38%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>13→7</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1488,23 +1488,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1284336467</v>
+        <v>-506599353</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>6.79%→7.79%</t>
+          <t>0.51%→0.42%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1516,23 +1516,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-506599384</v>
+        <v>-894873271</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.42%</t>
+          <t>4.88%→4.49%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>158→152</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>-4</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-115947042</v>
+        <v>-115947035</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>-3</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-480139674</v>
+        <v>-480139645</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>-3</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-979603856</v>
+        <v>-979603797</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>-3</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-811629295</v>
+        <v>-811629246</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,174억   ·   현금 51억(1.7%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 6종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,017억   ·   현금 26억(0.8%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1747,7 +1747,7 @@
         <v>72</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>900575728</v>
+        <v>900576102</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>-176</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1618407511</v>
+        <v>-1618408183</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>63</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1106878166</v>
+        <v>1106878625</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>-122</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-833467148</v>
+        <v>-833467494</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>17</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>318503404</v>
+        <v>318503536</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>-16</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-771679767</v>
+        <v>-771680087</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>13</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>289035413</v>
+        <v>289035533</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>-10</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-675219796</v>
+        <v>-675220076</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>12</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>276659916</v>
+        <v>276660031</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>4</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>249311925</v>
+        <v>249312028</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,664억   ·   현금 77억(2.8%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 9종목  /  매도 14종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,650억   ·   현금 38억(1.4%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 9종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2068,7 +2068,7 @@
         <v>46</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>6567692820</v>
+        <v>6557758410</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>-195</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-1224501907</v>
+        <v>-1222649704</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>36</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1894160683</v>
+        <v>1891295542</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>-149</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-4146384893</v>
+        <v>-4140112996</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>31</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1262244989</v>
+        <v>1260335694</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>-96</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-1545152852</v>
+        <v>-1542815626</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>21</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>3636820239</v>
+        <v>3631319120</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>-80</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-1488571279</v>
+        <v>-1486319640</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>19</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>774889925</v>
+        <v>773717812</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>-66</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-1223708708</v>
+        <v>-1221857704</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>15</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>844757591</v>
+        <v>843479796</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>-53</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-1299723671</v>
+        <v>-1297757685</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>14</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>1230781404</v>
+        <v>1228919702</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>-50</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-966712032</v>
+        <v>-965249766</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>13</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>4244939945</v>
+        <v>4238518972</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>-39</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-2345887864</v>
+        <v>-2342339432</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>10</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>2177993946</v>
+        <v>2174699473</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>-33</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-1247702996</v>
+        <v>-1245815698</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>-30</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1441640302</v>
+        <v>-1439459651</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>-30</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1622093215</v>
+        <v>-1619639607</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>-26</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-1374879334</v>
+        <v>-1372799667</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>-18</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-2671099707</v>
+        <v>-2667059353</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>-6</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-1082717476</v>
+        <v>-1081079738</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,028억   ·   현금 13억(0.7%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 6종목  /  매도 6종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,933억   ·   현금 6억(0.3%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B64" s="4" t="n"/>
@@ -2693,7 +2693,7 @@
         <v>125</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2132830248</v>
+        <v>2132831696</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>-357</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-4532630520</v>
+        <v>-4532633597</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>121</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>8327833186</v>
+        <v>8327838839</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>-113</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-1010564175</v>
+        <v>-1010564861</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>108</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>928621364</v>
+        <v>928621994</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>-103</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-3589857313</v>
+        <v>-3589859750</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>59</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>994267533</v>
+        <v>994268208</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>-62</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-996144232</v>
+        <v>-996144908</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>54</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>899666577</v>
+        <v>899667188</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>-12</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-107086750</v>
+        <v>-107086822</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>257950379</v>
+        <v>257950554</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>-12</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-2081987022</v>
+        <v>-2081988435</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 306억   ·   현금 46억(13.1%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 5종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 306억   ·   현금 7억(2.3%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 5종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B74" s="4" t="n"/>
@@ -3046,11 +3046,11 @@
         <v>89</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>93019240</v>
+        <v>92293000</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.31%</t>
+          <t>0.00%→0.30%</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -3067,11 +3067,11 @@
         <v>-110</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-81083200</v>
+        <v>-81532000</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>1.62%→1.36%</t>
+          <t>1.63%→1.37%</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -3090,11 +3090,11 @@
         <v>42</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>13337520</v>
+        <v>12880560</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.74%</t>
+          <t>2.59%→2.64%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -3111,11 +3111,11 @@
         <v>-60</v>
       </c>
       <c r="I78" s="15" t="n">
-        <v>-54141600</v>
+        <v>-51204000</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.48%</t>
+          <t>0.62%→0.45%</t>
         </is>
       </c>
       <c r="K78" s="13" t="inlineStr">
@@ -3134,11 +3134,11 @@
         <v>16</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>37971200</v>
+        <v>35414400</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>1.11%→1.24%</t>
+          <t>1.03%→1.16%</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
@@ -3155,11 +3155,11 @@
         <v>-21</v>
       </c>
       <c r="I79" s="15" t="n">
-        <v>-35271600</v>
+        <v>-35985600</v>
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>2.77%→2.67%</t>
+          <t>2.82%→2.72%</t>
         </is>
       </c>
       <c r="K79" s="13" t="inlineStr">
@@ -3178,11 +3178,11 @@
         <v>5</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>78710000</v>
+        <v>76330000</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.25%</t>
+          <t>0.95%→1.21%</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
@@ -3199,11 +3199,11 @@
         <v>-17</v>
       </c>
       <c r="I80" s="15" t="n">
-        <v>-27744000</v>
+        <v>-28553200</v>
       </c>
       <c r="J80" s="16" t="inlineStr">
         <is>
-          <t>4.66%→4.59%</t>
+          <t>4.79%→4.72%</t>
         </is>
       </c>
       <c r="K80" s="13" t="inlineStr">
@@ -3222,11 +3222,11 @@
         <v>5</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>47600000</v>
+        <v>50694000</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>2.70%→2.87%</t>
+          <t>2.87%→3.05%</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
@@ -3243,11 +3243,11 @@
         <v>-12</v>
       </c>
       <c r="I81" s="15" t="n">
-        <v>-47409600</v>
+        <v>-48388800</v>
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>1.33%→1.18%</t>
+          <t>1.35%→1.20%</t>
         </is>
       </c>
       <c r="K81" s="13" t="inlineStr">
@@ -3271,11 +3271,11 @@
         <v>-10</v>
       </c>
       <c r="I82" s="15" t="n">
-        <v>-54944000</v>
+        <v>-53448000</v>
       </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.91%</t>
+          <t>1.05%→0.88%</t>
         </is>
       </c>
       <c r="K82" s="13" t="inlineStr">
@@ -3299,11 +3299,11 @@
         <v>-5</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>-42092000</v>
+        <v>-45220000</v>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>2.49%→2.37%</t>
+          <t>2.68%→2.54%</t>
         </is>
       </c>
       <c r="K83" s="13" t="inlineStr">
@@ -3327,11 +3327,11 @@
         <v>-5</v>
       </c>
       <c r="I84" s="15" t="n">
-        <v>-68510000</v>
+        <v>-73440000</v>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
-          <t>3.34%→3.13%</t>
+          <t>3.57%→3.35%</t>
         </is>
       </c>
       <c r="K84" s="13" t="inlineStr">
@@ -3360,7 +3360,7 @@
     <row r="88" ht="19" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,107억      오늘 2026-10-14  vs  5일전 2026-10-06      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,051억      오늘 2026-10-14  vs  5일전 2026-10-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B88" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261014.xlsx
+++ b/reports/pdf_rolling5_20261014.xlsx
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-326871539</v>
+        <v>-1168191154</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.49%→1.55%</t>
+          <t>1.55%→1.06%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>701→673</t>
+          <t>157→129</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1168191154</v>
+        <v>-326871539</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.06%</t>
+          <t>1.49%→1.55%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>157→129</t>
+          <t>701→673</t>
         </is>
       </c>
     </row>
@@ -1404,23 +1404,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1284336389</v>
+        <v>-1557852472</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>6.79%→7.79%</t>
+          <t>0.57%→0.36%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>13→7</t>
         </is>
       </c>
     </row>
@@ -1432,23 +1432,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1557852472</v>
+        <v>-506599353</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.57%→0.36%</t>
+          <t>0.51%→0.42%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>13→7</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1460,23 +1460,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-127244439</v>
+        <v>-894873271</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.38%</t>
+          <t>4.88%→4.49%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>158→152</t>
         </is>
       </c>
     </row>
@@ -1488,23 +1488,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-506599353</v>
+        <v>-1284336389</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.42%</t>
+          <t>6.79%→7.79%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1516,23 +1516,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-894873271</v>
+        <v>-127244439</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>4.88%→4.49%</t>
+          <t>0.42%→0.38%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>158→152</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1572,23 +1572,23 @@
       <c r="E32" s="17" t="n"/>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H32" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-480139645</v>
+        <v>-979603797</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>5.99%→5.70%</t>
+          <t>2.57%→2.91%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -1600,23 +1600,23 @@
       <c r="E33" s="17" t="n"/>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-979603797</v>
+        <v>-480139645</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.91%</t>
+          <t>5.99%→5.70%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -2462,18 +2462,18 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>쎄트렉아이  (편출)</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1439459651</v>
+        <v>-1619639607</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.00%</t>
+          <t>0.58%→0.00%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2490,18 +2490,18 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>쎄트렉아이  (편출)</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1619639607</v>
+        <v>-1439459651</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.00%</t>
+          <t>0.52%→0.00%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2883,23 +2883,23 @@
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-107086822</v>
+        <v>-2081988435</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>3.43%→3.12%</t>
+          <t>8.24%→7.39%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>686→674</t>
+          <t>94→82</t>
         </is>
       </c>
     </row>
@@ -2927,23 +2927,23 @@
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-2081988435</v>
+        <v>-107086822</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>8.24%→7.39%</t>
+          <t>3.43%→3.12%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>94→82</t>
+          <t>686→674</t>
         </is>
       </c>
     </row>
@@ -3171,23 +3171,23 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>76330000</v>
+        <v>50694000</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>0.95%→1.21%</t>
+          <t>2.87%→3.05%</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -3215,23 +3215,23 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B81" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>50694000</v>
+        <v>76330000</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>2.87%→3.05%</t>
+          <t>0.95%→1.21%</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261014.xlsx
+++ b/reports/pdf_rolling5_20261014.xlsx
@@ -1432,23 +1432,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-506599353</v>
+        <v>-127244439</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.42%</t>
+          <t>0.42%→0.38%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1460,23 +1460,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-894873271</v>
+        <v>-506599353</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>4.88%→4.49%</t>
+          <t>0.51%→0.42%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>158→152</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1488,23 +1488,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1284336389</v>
+        <v>-894873271</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>6.79%→7.79%</t>
+          <t>4.88%→4.49%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>158→152</t>
         </is>
       </c>
     </row>
@@ -1516,23 +1516,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-127244439</v>
+        <v>-1284336389</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.38%</t>
+          <t>6.79%→7.79%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1572,23 +1572,23 @@
       <c r="E32" s="17" t="n"/>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H32" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-979603797</v>
+        <v>-480139645</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.91%</t>
+          <t>5.99%→5.70%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -1600,23 +1600,23 @@
       <c r="E33" s="17" t="n"/>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-480139645</v>
+        <v>-811629246</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>5.99%→5.70%</t>
+          <t>0.85%→0.64%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>15→12</t>
         </is>
       </c>
     </row>
@@ -1628,23 +1628,23 @@
       <c r="E34" s="17" t="n"/>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-811629246</v>
+        <v>-979603797</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.64%</t>
+          <t>2.57%→2.91%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>15→12</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 306억   ·   현금 7억(2.3%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 5종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 306억   ·   현금 4억(1.1%)      오늘 2026-10-14  vs  5일전 2026-10-06      매수 5종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B74" s="4" t="n"/>
@@ -3292,23 +3292,23 @@
       <c r="E83" s="17" t="n"/>
       <c r="G83" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H83" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>-45220000</v>
+        <v>-73440000</v>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>2.68%→2.54%</t>
+          <t>3.57%→3.35%</t>
         </is>
       </c>
       <c r="K83" s="13" t="inlineStr">
         <is>
-          <t>90→85</t>
+          <t>74→69</t>
         </is>
       </c>
     </row>
@@ -3320,23 +3320,23 @@
       <c r="E84" s="17" t="n"/>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H84" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I84" s="15" t="n">
-        <v>-73440000</v>
+        <v>-45220000</v>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
-          <t>3.57%→3.35%</t>
+          <t>2.68%→2.54%</t>
         </is>
       </c>
       <c r="K84" s="13" t="inlineStr">
         <is>
-          <t>74→69</t>
+          <t>90→85</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261014.xlsx
+++ b/reports/pdf_rolling5_20261014.xlsx
@@ -1404,23 +1404,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1557852472</v>
+        <v>-506599353</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>0.57%→0.36%</t>
+          <t>0.51%→0.42%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>13→7</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1432,23 +1432,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-127244439</v>
+        <v>-1284336389</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.38%</t>
+          <t>6.79%→7.79%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1460,23 +1460,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-506599353</v>
+        <v>-127244439</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.42%</t>
+          <t>0.42%→0.38%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1516,23 +1516,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1284336389</v>
+        <v>-1557852472</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>6.79%→7.79%</t>
+          <t>0.57%→0.36%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>13→7</t>
         </is>
       </c>
     </row>
@@ -1600,23 +1600,23 @@
       <c r="E33" s="17" t="n"/>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-811629246</v>
+        <v>-979603797</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.64%</t>
+          <t>2.57%→2.91%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>15→12</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -1628,23 +1628,23 @@
       <c r="E34" s="17" t="n"/>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-979603797</v>
+        <v>-811629246</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.91%</t>
+          <t>0.85%→0.64%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>15→12</t>
         </is>
       </c>
     </row>
@@ -3171,23 +3171,23 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>50694000</v>
+        <v>76330000</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>2.87%→3.05%</t>
+          <t>0.95%→1.21%</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -3215,23 +3215,23 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B81" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>76330000</v>
+        <v>50694000</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>0.95%→1.21%</t>
+          <t>2.87%→3.05%</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -3292,23 +3292,23 @@
       <c r="E83" s="17" t="n"/>
       <c r="G83" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H83" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>-73440000</v>
+        <v>-45220000</v>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>3.57%→3.35%</t>
+          <t>2.68%→2.54%</t>
         </is>
       </c>
       <c r="K83" s="13" t="inlineStr">
         <is>
-          <t>74→69</t>
+          <t>90→85</t>
         </is>
       </c>
     </row>
@@ -3320,23 +3320,23 @@
       <c r="E84" s="17" t="n"/>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H84" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I84" s="15" t="n">
-        <v>-45220000</v>
+        <v>-73440000</v>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
-          <t>2.68%→2.54%</t>
+          <t>3.57%→3.35%</t>
         </is>
       </c>
       <c r="K84" s="13" t="inlineStr">
         <is>
-          <t>90→85</t>
+          <t>74→69</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261014.xlsx
+++ b/reports/pdf_rolling5_20261014.xlsx
@@ -1572,23 +1572,23 @@
       <c r="E32" s="17" t="n"/>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H32" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-480139645</v>
+        <v>-979603797</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>5.99%→5.70%</t>
+          <t>2.57%→2.91%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -1600,23 +1600,23 @@
       <c r="E33" s="17" t="n"/>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-979603797</v>
+        <v>-480139645</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.91%</t>
+          <t>5.99%→5.70%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -2462,18 +2462,18 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>쎄트렉아이  (편출)</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1619639607</v>
+        <v>-1439459651</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.00%</t>
+          <t>0.52%→0.00%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2490,18 +2490,18 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>쎄트렉아이  (편출)</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1439459651</v>
+        <v>-1619639607</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.00%</t>
+          <t>0.58%→0.00%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -3292,23 +3292,23 @@
       <c r="E83" s="17" t="n"/>
       <c r="G83" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H83" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>-45220000</v>
+        <v>-73440000</v>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>2.68%→2.54%</t>
+          <t>3.57%→3.35%</t>
         </is>
       </c>
       <c r="K83" s="13" t="inlineStr">
         <is>
-          <t>90→85</t>
+          <t>74→69</t>
         </is>
       </c>
     </row>
@@ -3320,23 +3320,23 @@
       <c r="E84" s="17" t="n"/>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H84" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I84" s="15" t="n">
-        <v>-73440000</v>
+        <v>-45220000</v>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
-          <t>3.57%→3.35%</t>
+          <t>2.68%→2.54%</t>
         </is>
       </c>
       <c r="K84" s="13" t="inlineStr">
         <is>
-          <t>74→69</t>
+          <t>90→85</t>
         </is>
       </c>
     </row>
